--- a/reports/biggirls/CJ_Girls_Catalog_2026-10-06.xlsx
+++ b/reports/biggirls/CJ_Girls_Catalog_2026-10-06.xlsx
@@ -6575,13 +6575,13 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>10</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>10</v>
@@ -6599,7 +6599,7 @@
         <v>12</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>10.2</v>
+        <v>9.6</v>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
@@ -6618,76 +6618,76 @@
         <v>12</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>7</v>
+        <v>5.95</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>7</v>
+        <v>5.95</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>7</v>
+        <v>5.95</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>7</v>
+        <v>5.95</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>7</v>
+        <v>5.95</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>7</v>
+        <v>5.95</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>7</v>
+        <v>5.95</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>7</v>
+        <v>5.95</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>7</v>
+        <v>5.95</v>
       </c>
       <c r="X5" s="6" t="n">
-        <v>7</v>
+        <v>5.95</v>
       </c>
       <c r="Y5" s="6" t="n">
-        <v>7</v>
+        <v>5.95</v>
       </c>
       <c r="Z5" s="6" t="n">
-        <v>7</v>
+        <v>5.95</v>
       </c>
       <c r="AA5" s="6" t="n">
-        <v>7</v>
+        <v>5.95</v>
       </c>
       <c r="AB5" s="6" t="n">
-        <v>7</v>
+        <v>5.95</v>
       </c>
       <c r="AC5" s="6" t="n">
-        <v>7</v>
+        <v>5.95</v>
       </c>
       <c r="AD5" s="6" t="n">
-        <v>7</v>
+        <v>5.95</v>
       </c>
       <c r="AE5" s="6" t="n">
-        <v>7</v>
+        <v>5.95</v>
       </c>
       <c r="AF5" s="6" t="n">
-        <v>7</v>
+        <v>5.95</v>
       </c>
       <c r="AG5" s="6" t="n">
-        <v>7</v>
+        <v>5.95</v>
       </c>
       <c r="AH5" s="6" t="n">
-        <v>7</v>
+        <v>5.95</v>
       </c>
       <c r="AI5" s="6" t="n">
-        <v>7</v>
+        <v>5.95</v>
       </c>
       <c r="AJ5" s="6" t="n">
-        <v>7</v>
+        <v>5.95</v>
       </c>
       <c r="AK5" s="6" t="n">
-        <v>7</v>
+        <v>5.95</v>
       </c>
       <c r="AL5" s="6" t="n">
-        <v>7</v>
+        <v>5.95</v>
       </c>
       <c r="AM5" s="6" t="n">
         <v>8</v>
@@ -8799,7 +8799,7 @@
         <v>20</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="J5" s="6" t="n">
         <v>18</v>
@@ -10139,16 +10139,16 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>10</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>10.2</v>
+        <v>9.6</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>8.5</v>
@@ -10159,9 +10159,15 @@
       <c r="H5" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="I5" s="7" t="inlineStr"/>
-      <c r="J5" s="7" t="inlineStr"/>
-      <c r="K5" s="7" t="inlineStr"/>
+      <c r="I5" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>20</v>
+      </c>
       <c r="L5" s="6" t="n">
         <v>18</v>
       </c>
@@ -10267,16 +10273,20 @@
         <v>12</v>
       </c>
       <c r="AT5" s="6" t="n">
-        <v>7</v>
+        <v>5.95</v>
       </c>
       <c r="AU5" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="AV5" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW5" s="6" t="n">
-        <v>7</v>
+      <c r="AV5" s="7" t="inlineStr">
+        <is>
+          <t>5.95 - 7.00</t>
+        </is>
+      </c>
+      <c r="AW5" s="7" t="inlineStr">
+        <is>
+          <t>5.95 - 7.00</t>
+        </is>
       </c>
       <c r="AX5" s="6" t="n">
         <v>5</v>
@@ -10293,8 +10303,10 @@
       <c r="BB5" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="BC5" s="6" t="n">
-        <v>5</v>
+      <c r="BC5" s="7" t="inlineStr">
+        <is>
+          <t>4.25 - 5.00</t>
+        </is>
       </c>
       <c r="BD5" s="6" t="n">
         <v>20</v>
@@ -10306,7 +10318,7 @@
         <v>17</v>
       </c>
       <c r="BG5" s="6" t="n">
-        <v>12.75</v>
+        <v>12</v>
       </c>
       <c r="BH5" s="6" t="n">
         <v>17</v>
@@ -10342,20 +10354,20 @@
       </c>
       <c r="BR5" s="7" t="inlineStr">
         <is>
-          <t>6.80 - 8.00</t>
+          <t>6.40 - 8.00</t>
         </is>
       </c>
       <c r="BS5" s="6" t="n">
         <v>6</v>
       </c>
       <c r="BT5" s="6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BU5" s="6" t="n">
-        <v>12.6</v>
+        <v>11.7</v>
       </c>
       <c r="BV5" s="6" t="n">
-        <v>12.6</v>
+        <v>11.7</v>
       </c>
       <c r="BW5" s="6" t="n">
         <v>20</v>
@@ -10367,7 +10379,7 @@
         <v>20</v>
       </c>
       <c r="BZ5" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CA5" s="6" t="n">
         <v>17</v>
@@ -12990,7 +13002,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>17.00 - 20.00</t>
+          <t>16.00 - 20.00</t>
         </is>
       </c>
       <c r="C5" s="6" t="n">
@@ -13000,7 +13012,7 @@
         <v>17</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>25</v>
@@ -13015,7 +13027,7 @@
         <v>20</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>17</v>
@@ -13038,7 +13050,9 @@
       <c r="Q5" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="R5" s="7" t="inlineStr"/>
+      <c r="R5" s="6" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="6" ht="33" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -13581,18 +13595,20 @@
           <t>Retail Price</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr"/>
+      <c r="B5" s="6" t="n">
+        <v>30</v>
+      </c>
       <c r="C5" s="6" t="n">
         <v>30</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>21.25</v>
+        <v>20</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>21.25</v>
+        <v>20</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>30</v>
